--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M17B5_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M17B5_IN_Piura.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>21.37</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" s="31">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>49.69</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>28.35</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.59</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1919,11 +1919,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>74.0279</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>52.602</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>71.06</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1969,11 +1969,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>21.4259</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>28.94</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>74.0654</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2271,6 +2271,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2556,6 +2557,7 @@
       <c r="F18" s="17" t="inlineStr"/>
       <c r="G18" s="17" t="inlineStr"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -2600,6 +2602,7 @@
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="180" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
@@ -3054,11 +3057,11 @@
       </c>
       <c r="B19" s="33">
         <f>SUM(B10:B18)</f>
-        <v/>
+        <v>875.24</v>
       </c>
       <c r="C19" s="23">
         <f>SUM(C10:C18)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
@@ -3068,19 +3071,19 @@
       <c r="E19" s="17" t="inlineStr"/>
       <c r="F19" s="17">
         <f>ROUND(AVERAGE(F10:F18),2)</f>
-        <v/>
+        <v>22.85</v>
       </c>
       <c r="G19" s="22">
         <f>ROUND(AVERAGE(G10:G18),4)</f>
-        <v/>
+        <v>0.451</v>
       </c>
       <c r="H19" s="23">
         <f>ROUND(AVERAGE(H10:H18),2)</f>
-        <v/>
+        <v>29.59</v>
       </c>
       <c r="I19" s="23">
         <f>ROUND(AVERAGE(I10:I18),2)</f>
-        <v/>
+        <v>69.38</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
